--- a/docs/Sprint 3/deliverables/10-S3-dedication.xlsx
+++ b/docs/Sprint 3/deliverables/10-S3-dedication.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4700CC28-6D58-4809-94E4-E5B6CB49B7CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{02C8C9D8-2F21-45BA-9A66-91BB45160C54}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{02C8C9D8-2F21-45BA-9A66-91BB45160C54}"/>
   </bookViews>
   <sheets>
     <sheet name="Contribución a los entregables" sheetId="1" r:id="rId1"/>
@@ -440,6 +440,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="46" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -451,15 +460,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="46" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="46" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1767,34 +1767,34 @@
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="23" t="s">
+      <c r="B33" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
     </row>
     <row r="34" spans="2:7" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="23" t="s">
+      <c r="B34" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
     </row>
     <row r="35" spans="2:7" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="23" t="s">
+      <c r="B35" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="23"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
     </row>
     <row r="36" spans="2:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1845,11 +1845,11 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" ht="101.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E3" s="11"/>
@@ -2498,11 +2498,11 @@
       <c r="H27" s="2"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
       <c r="H28" s="6">
         <f>SUM(H2:H21)/20</f>
         <v>1.0000000000000002</v>
@@ -2633,7 +2633,7 @@
       <c r="C2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="22">
         <v>1.3212152777777777</v>
       </c>
       <c r="E2" s="17">
@@ -2659,7 +2659,7 @@
       <c r="C3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="23">
         <v>0.87565972222222221</v>
       </c>
       <c r="E3" s="17">
@@ -2685,7 +2685,7 @@
       <c r="C4" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="24">
         <v>1.0733333333333333</v>
       </c>
       <c r="E4" s="17">
@@ -2711,7 +2711,7 @@
       <c r="C5" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="23">
         <v>0.79408564814814819</v>
       </c>
       <c r="E5" s="17">
@@ -2737,7 +2737,7 @@
       <c r="C6" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="23">
         <v>0.91697916666666668</v>
       </c>
       <c r="E6" s="17">
@@ -2763,7 +2763,7 @@
       <c r="C7" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="23">
         <v>0.9202893518518519</v>
       </c>
       <c r="E7" s="17">
@@ -2790,7 +2790,7 @@
       <c r="C8" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="23">
         <v>0.97291666666666665</v>
       </c>
       <c r="E8" s="17">
@@ -2816,7 +2816,7 @@
       <c r="C9" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="23">
         <v>0.76469907407407411</v>
       </c>
       <c r="E9" s="17">
@@ -2842,7 +2842,7 @@
       <c r="C10" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="23">
         <v>0.81597222222222221</v>
       </c>
       <c r="E10" s="17">
@@ -2868,7 +2868,7 @@
       <c r="C11" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="23">
         <v>0.83481481481481479</v>
       </c>
       <c r="E11" s="17">
@@ -2894,7 +2894,7 @@
       <c r="C12" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="23">
         <v>0.75748842592592591</v>
       </c>
       <c r="E12" s="17">
@@ -2920,7 +2920,7 @@
       <c r="C13" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="23">
         <v>0.875</v>
       </c>
       <c r="E13" s="17">
@@ -2946,7 +2946,7 @@
       <c r="C14" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="23">
         <v>0.93865740740740744</v>
       </c>
       <c r="E14" s="17">
@@ -2973,7 +2973,7 @@
       <c r="C15" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="24">
         <v>1.0462615740740742</v>
       </c>
       <c r="E15" s="17">
@@ -2999,7 +2999,7 @@
       <c r="C16" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="23">
         <v>0.7492361111111111</v>
       </c>
       <c r="E16" s="17">
@@ -3025,7 +3025,7 @@
       <c r="C17" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="23">
         <v>0.80880787037037039</v>
       </c>
       <c r="E17" s="17">
@@ -3051,7 +3051,7 @@
       <c r="C18" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="23">
         <v>0.95706018518518521</v>
       </c>
       <c r="E18" s="17">
@@ -3077,7 +3077,7 @@
       <c r="C19" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="23">
         <v>0.79861111111111116</v>
       </c>
       <c r="E19" s="17">
@@ -3103,7 +3103,7 @@
       <c r="C20" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="23">
         <v>0.84755787037037034</v>
       </c>
       <c r="E20" s="17">
@@ -3129,7 +3129,7 @@
       <c r="C21" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="23">
         <v>0.75665509259259256</v>
       </c>
       <c r="E21" s="17">
@@ -3212,11 +3212,11 @@
       <c r="H27" s="2"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
       <c r="H28" s="6">
         <f>SUM(H2:H21)/20</f>
         <v>1.0000000000000004</v>
@@ -3309,9 +3309,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3477,19 +3480,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D0D844A-E87E-42E2-B155-132CABE67861}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F4B272D-551A-4AF9-B220-C688C9745ED1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3513,9 +3512,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F4B272D-551A-4AF9-B220-C688C9745ED1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D0D844A-E87E-42E2-B155-132CABE67861}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/docs/Sprint 3/deliverables/10-S3-dedication.xlsx
+++ b/docs/Sprint 3/deliverables/10-S3-dedication.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sergi\Desktop\ISPP-G8\ISPP-G8\docs\Sprint 3\deliverables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4700CC28-6D58-4809-94E4-E5B6CB49B7CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD0C919F-4E42-493F-A712-E45ABBF9BB05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{02C8C9D8-2F21-45BA-9A66-91BB45160C54}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{02C8C9D8-2F21-45BA-9A66-91BB45160C54}"/>
   </bookViews>
   <sheets>
     <sheet name="Contribución a los entregables" sheetId="1" r:id="rId1"/>
@@ -1261,7 +1261,7 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="F2" s="3">
-        <v>1.3552190749318194</v>
+        <v>1.4248733019863706</v>
       </c>
       <c r="G2" s="3"/>
     </row>
@@ -1282,7 +1282,7 @@
         <v>0.84</v>
       </c>
       <c r="F3" s="3">
-        <v>0.94014834299243988</v>
+        <v>0.99243524259961902</v>
       </c>
       <c r="G3" s="3"/>
     </row>
@@ -1303,7 +1303,7 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="F4" s="3">
-        <v>1.0839529727959263</v>
+        <v>1.2609408834454818</v>
       </c>
       <c r="G4" s="3"/>
     </row>
@@ -1324,7 +1324,7 @@
         <v>0.79</v>
       </c>
       <c r="F5" s="3">
-        <v>1.0626757142027177</v>
+        <v>0.69048790886468936</v>
       </c>
       <c r="G5" s="3"/>
     </row>
@@ -1345,7 +1345,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="F6" s="3">
-        <v>1.0308313960390789</v>
+        <v>1.074872192111006</v>
       </c>
       <c r="G6" s="3"/>
     </row>
@@ -1366,7 +1366,7 @@
         <v>0.89</v>
       </c>
       <c r="F7" s="3">
-        <v>1.033239506825647</v>
+        <v>1.0495057992901389</v>
       </c>
       <c r="G7" s="3"/>
     </row>
@@ -1387,7 +1387,7 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="F8" s="3">
-        <v>1.0715251003449662</v>
+        <v>1.1118654861675086</v>
       </c>
       <c r="G8" s="3"/>
     </row>
@@ -1408,7 +1408,7 @@
         <v>0.84</v>
       </c>
       <c r="F9" s="3">
-        <v>0.92004987988915965</v>
+        <v>0.89149781890355018</v>
       </c>
       <c r="G9" s="3"/>
     </row>
@@ -1429,7 +1429,7 @@
         <v>1.18</v>
       </c>
       <c r="F10" s="3">
-        <v>0.89672656912414661</v>
+        <v>0.92540642487712899</v>
       </c>
       <c r="G10" s="3"/>
     </row>
@@ -1450,7 +1450,7 @@
         <v>1.22</v>
       </c>
       <c r="F11" s="3">
-        <v>1.0619936968121162</v>
+        <v>1.0480897514108811</v>
       </c>
       <c r="G11" s="3"/>
     </row>
@@ -1471,7 +1471,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="3">
-        <v>0.8541804719055146</v>
+        <v>0.85917365569216797</v>
       </c>
       <c r="G12" s="3"/>
     </row>
@@ -1492,7 +1492,7 @@
         <v>0.6</v>
       </c>
       <c r="F13" s="3">
-        <v>0.9396684048286833</v>
+        <v>0.85422131527119616</v>
       </c>
       <c r="G13" s="3"/>
     </row>
@@ -1513,7 +1513,7 @@
         <v>0.81</v>
       </c>
       <c r="F14" s="3">
-        <v>1.0466019957007646</v>
+        <v>1.0616531938003129</v>
       </c>
       <c r="G14" s="3"/>
     </row>
@@ -1534,7 +1534,7 @@
         <v>0.95</v>
       </c>
       <c r="F15" s="3">
-        <v>1.064258668146336</v>
+        <v>1.1052598141685925</v>
       </c>
       <c r="G15" s="3"/>
     </row>
@@ -1555,7 +1555,7 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="F16" s="3">
-        <v>0.84817703487466467</v>
+        <v>0.96393823581866334</v>
       </c>
       <c r="G16" s="3"/>
     </row>
@@ -1576,7 +1576,7 @@
         <v>0.94</v>
       </c>
       <c r="F17" s="3">
-        <v>0.89151460906510593</v>
+        <v>0.94822393151533213</v>
       </c>
       <c r="G17" s="3"/>
     </row>
@@ -1597,7 +1597,7 @@
         <v>1.03</v>
       </c>
       <c r="F18" s="3">
-        <v>1.0599897444792379</v>
+        <v>1.0738235512490693</v>
       </c>
       <c r="G18" s="3"/>
     </row>
@@ -1618,7 +1618,7 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="F19" s="3">
-        <v>0.9447203854998053</v>
+        <v>0.94148048188492062</v>
       </c>
       <c r="G19" s="3"/>
     </row>
@@ -1639,7 +1639,7 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="F20" s="3">
-        <v>0.98032842926342967</v>
+        <v>1.0014060972725387</v>
       </c>
       <c r="G20" s="3"/>
     </row>
@@ -1660,7 +1660,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="F21" s="3">
-        <v>0.91419800227844339</v>
+        <v>0.72084491367083237</v>
       </c>
       <c r="G21" s="3"/>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="F28" s="6">
         <f>SUM(F2:F25)/$B$27</f>
-        <v>1.0000000000000004</v>
+        <v>1</v>
       </c>
       <c r="G28" s="6">
         <f>SUM(G2:G25)/$B$27</f>
@@ -2641,15 +2641,15 @@
         <v>1.5854583333333332</v>
       </c>
       <c r="F2" s="20">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="G2" s="20">
         <f>((E2*10)+F2)/2</f>
-        <v>11.177291666666665</v>
+        <v>12.927291666666665</v>
       </c>
       <c r="H2" s="3">
         <f>G2 / AVERAGE($G$2:$G$21)</f>
-        <v>1.3552190749318194</v>
+        <v>1.4248733019863706</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2667,15 +2667,15 @@
         <v>1.0507916666666666</v>
       </c>
       <c r="F3" s="20">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="G3" s="20">
         <f t="shared" ref="G3:G21" si="1">((E3*10)+F3)/2</f>
-        <v>7.7539583333333333</v>
+        <v>9.0039583333333333</v>
       </c>
       <c r="H3" s="3">
         <f t="shared" ref="H3:H21" si="2">G3 / AVERAGE($G$2:$G$21)</f>
-        <v>0.94014834299243988</v>
+        <v>0.99243524259961902</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2693,15 +2693,15 @@
         <v>1.2879999999999998</v>
       </c>
       <c r="F4" s="20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G4" s="20">
         <f t="shared" si="1"/>
-        <v>8.94</v>
+        <v>11.44</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" si="2"/>
-        <v>1.0839529727959263</v>
+        <v>1.2609408834454818</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2719,15 +2719,15 @@
         <v>0.95290277777777777</v>
       </c>
       <c r="F5" s="20">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G5" s="20">
         <f t="shared" si="1"/>
-        <v>8.7645138888888887</v>
+        <v>6.2645138888888887</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="2"/>
-        <v>1.0626757142027177</v>
+        <v>0.69048790886468936</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2745,15 +2745,15 @@
         <v>1.1003750000000001</v>
       </c>
       <c r="F6" s="20">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="G6" s="20">
         <f t="shared" si="1"/>
-        <v>8.5018750000000001</v>
+        <v>9.7518750000000001</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" si="2"/>
-        <v>1.0308313960390789</v>
+        <v>1.074872192111006</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2771,15 +2771,15 @@
         <v>1.1043472222222221</v>
       </c>
       <c r="F7" s="20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G7" s="20">
         <f t="shared" si="1"/>
-        <v>8.5217361111111103</v>
+        <v>9.5217361111111103</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" si="2"/>
-        <v>1.033239506825647</v>
+        <v>1.0495057992901389</v>
       </c>
       <c r="L7" s="18"/>
     </row>
@@ -2798,15 +2798,15 @@
         <v>1.1675</v>
       </c>
       <c r="F8" s="20">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="G8" s="20">
         <f t="shared" si="1"/>
-        <v>8.8375000000000004</v>
+        <v>10.0875</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" si="2"/>
-        <v>1.0715251003449662</v>
+        <v>1.1118654861675086</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2824,15 +2824,15 @@
         <v>0.91763888888888889</v>
       </c>
       <c r="F9" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G9" s="20">
         <f t="shared" si="1"/>
-        <v>7.5881944444444445</v>
+        <v>8.0881944444444436</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="2"/>
-        <v>0.92004987988915965</v>
+        <v>0.89149781890355018</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2850,15 +2850,15 @@
         <v>0.97916666666666663</v>
       </c>
       <c r="F10" s="20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G10" s="20">
         <f t="shared" si="1"/>
-        <v>7.395833333333333</v>
+        <v>8.3958333333333321</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="2"/>
-        <v>0.89672656912414661</v>
+        <v>0.92540642487712899</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2876,15 +2876,15 @@
         <v>1.0017777777777777</v>
       </c>
       <c r="F11" s="20">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="G11" s="20">
         <f t="shared" si="1"/>
-        <v>8.7588888888888885</v>
+        <v>9.5088888888888885</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" si="2"/>
-        <v>1.0619936968121162</v>
+        <v>1.0480897514108811</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2902,15 +2902,15 @@
         <v>0.90898611111111105</v>
       </c>
       <c r="F12" s="20">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="G12" s="20">
         <f t="shared" si="1"/>
-        <v>7.0449305555555553</v>
+        <v>7.7949305555555553</v>
       </c>
       <c r="H12" s="3">
         <f t="shared" si="2"/>
-        <v>0.8541804719055146</v>
+        <v>0.85917365569216797</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="H13" s="3">
         <f t="shared" si="2"/>
-        <v>0.9396684048286833</v>
+        <v>0.85422131527119616</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2954,15 +2954,15 @@
         <v>1.1263888888888889</v>
       </c>
       <c r="F14" s="20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G14" s="20">
         <f t="shared" si="1"/>
-        <v>8.6319444444444446</v>
+        <v>9.6319444444444446</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="2"/>
-        <v>1.0466019957007646</v>
+        <v>1.0616531938003129</v>
       </c>
       <c r="L14" s="19"/>
     </row>
@@ -2981,15 +2981,15 @@
         <v>1.255513888888889</v>
       </c>
       <c r="F15" s="20">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="G15" s="20">
         <f t="shared" si="1"/>
-        <v>8.7775694444444454</v>
+        <v>10.027569444444445</v>
       </c>
       <c r="H15" s="3">
         <f t="shared" si="2"/>
-        <v>1.064258668146336</v>
+        <v>1.1052598141685925</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3007,15 +3007,15 @@
         <v>0.89908333333333323</v>
       </c>
       <c r="F16" s="20">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="G16" s="20">
         <f t="shared" si="1"/>
-        <v>6.9954166666666664</v>
+        <v>8.7454166666666673</v>
       </c>
       <c r="H16" s="3">
         <f t="shared" si="2"/>
-        <v>0.84817703487466467</v>
+        <v>0.96393823581866334</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3033,15 +3033,15 @@
         <v>0.97056944444444448</v>
       </c>
       <c r="F17" s="20">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="G17" s="20">
         <f t="shared" si="1"/>
-        <v>7.3528472222222225</v>
+        <v>8.6028472222222234</v>
       </c>
       <c r="H17" s="3">
         <f t="shared" si="2"/>
-        <v>0.89151460906510593</v>
+        <v>0.94822393151533213</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3059,15 +3059,15 @@
         <v>1.1484722222222223</v>
       </c>
       <c r="F18" s="20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G18" s="20">
         <f t="shared" si="1"/>
-        <v>8.7423611111111121</v>
+        <v>9.7423611111111121</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="2"/>
-        <v>1.0599897444792379</v>
+        <v>1.0738235512490693</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3085,15 +3085,15 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="F19" s="20">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="G19" s="20">
         <f t="shared" si="1"/>
-        <v>7.791666666666667</v>
+        <v>8.5416666666666679</v>
       </c>
       <c r="H19" s="3">
         <f t="shared" si="2"/>
-        <v>0.9447203854998053</v>
+        <v>0.94148048188492062</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3111,15 +3111,15 @@
         <v>1.0170694444444444</v>
       </c>
       <c r="F20" s="20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G20" s="20">
         <f t="shared" si="1"/>
-        <v>8.0853472222222216</v>
+        <v>9.0853472222222216</v>
       </c>
       <c r="H20" s="3">
         <f t="shared" si="2"/>
-        <v>0.98032842926342967</v>
+        <v>1.0014060972725387</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3137,15 +3137,15 @@
         <v>0.90798611111111105</v>
       </c>
       <c r="F21" s="20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G21" s="20">
         <f t="shared" si="1"/>
-        <v>7.5399305555555554</v>
+        <v>6.5399305555555554</v>
       </c>
       <c r="H21" s="3">
         <f t="shared" si="2"/>
-        <v>0.91419800227844339</v>
+        <v>0.72084491367083237</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3219,7 +3219,7 @@
       <c r="E28" s="25"/>
       <c r="H28" s="6">
         <f>SUM(H2:H21)/20</f>
-        <v>1.0000000000000004</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -3309,15 +3309,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010099E9797445E2EA4280A45CB90FD95CBD" ma:contentTypeVersion="7" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="b362696dc43ecf0429c4c65f28c02171">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ba0fee18-8f7d-444d-be37-1e56d133d327" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="79fc1cf0b24a9b8e3e12f8f8264ba269" ns2:_="">
     <xsd:import namespace="ba0fee18-8f7d-444d-be37-1e56d133d327"/>
@@ -3479,6 +3470,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -3486,14 +3486,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F4B272D-551A-4AF9-B220-C688C9745ED1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC0DDDC5-E50E-4F26-8594-4A1786F565B7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3511,6 +3503,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F4B272D-551A-4AF9-B220-C688C9745ED1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D0D844A-E87E-42E2-B155-132CABE67861}">
   <ds:schemaRefs>
